--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Username: "admin", Password: "admin123"</t>
+          <t>Username: "admin"&lt;br&gt;Password: "admin123"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User is logged in, admin controls are visible</t>
+          <t>User should be logged in successfully and redirected to the main application view with admin controls visible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Username: "user", Password: "user123"</t>
+          <t>Username: "user"&lt;br&gt;Password: "user123"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User is logged in, admin controls are hidden</t>
+          <t>User should be logged in successfully and redirected to the main application view with read-only access (no admin controls)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Username: "invalid", Password: "invalid"</t>
+          <t>Username: "invalid"&lt;br&gt;Password: "wrong"</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error message: "Invalid credentials"</t>
+          <t>Alert message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User is logged out, login form is displayed</t>
+          <t>User should be logged out and returned to login screen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Click on "Add Row" button</t>
+          <t>Login as admin and click "Add Row" button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New empty row is added to the table</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify admin can edit an existing row</t>
+          <t>Verify admin can delete a row</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click "Edit" button on a row, modify data, click "Save"</t>
+          <t>Login as admin and click "Delete" button on a row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Row data is updated</t>
+          <t>The selected row should be removed from the table</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verify admin can delete a row</t>
+          <t>Verify admin can edit a row</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Click "Delete" button on a row</t>
+          <t>1. Login as admin&lt;br&gt;2. Click "Edit" button on a row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click "Save" button</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row is removed from the table</t>
+          <t>The row should become editable, then save changes and become read-only again</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify admin can save the table data</t>
+          <t>Verify admin can save the entire table</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Add/modify data, click "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes to table&lt;br&gt;3. Click "Save" button</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Success message: "Data saved successfully!"</t>
+          <t>Data should be saved to the server and success message displayed</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Date picker appears allowing date range selection</t>
+          <t>Date picker should appear allowing selection of date range</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verify data persistence after saving</t>
+          <t>Verify user cannot edit table data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Save data, logout, login again</t>
+          <t>Login as user and attempt to modify any field</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Previously saved data is displayed</t>
+          <t>All fields should be disabled/read-only</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verify user cannot modify data</t>
+          <t>Verify table loads correctly on login</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login as user, attempt to edit fields</t>
+          <t>Login with valid credentials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>All fields are disabled/read-only</t>
+          <t>Table should populate with data from the server</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verify empty table handling</t>
+          <t>Verify admin controls visibility for admin</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login with no existing data</t>
+          <t>Login as admin</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Empty table is displayed correctly</t>
+          <t>"Add Row" and "Save" buttons should be visible</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify saving empty table</t>
+          <t>Verify admin controls invisibility for user</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Try to save with no data</t>
+          <t>Login as user</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alert message: "No data to save."</t>
+          <t>"Add Row" and "Save" buttons should be hidden</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verify UI elements visibility for admin</t>
+          <t>Verify saving empty table</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>Login as admin, delete all rows, click "Save"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Add Row, Save buttons, and Actions column are visible</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verify UI elements visibility for user</t>
+          <t>Verify data persistence after logout and login</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes and save&lt;br&gt;3. Logout&lt;br&gt;4. Login again</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Add Row, Save buttons, and Actions column are hidden</t>
+          <t>Changes should persist and be visible after logging in again</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI adapts appropriately to screen size</t>
+          <t>Application should be responsive and usable on various screen sizes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verify performance with large data sets</t>
+          <t>Verify application load time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Load table with 100+ rows</t>
+          <t>Open the application URL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table loads within 3 seconds</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verify browser compatibility</t>
+          <t>Verify error handling for network issues</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Test on Chrome, Firefox, Safari, Edge</t>
+          <t>Disconnect network and attempt to save data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Application works consistently across browsers</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verify network error handling</t>
+          <t>Verify concurrent user access</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Disconnect network during save operation</t>
+          <t>Multiple users access the application simultaneously</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Appropriate error message displayed</t>
+          <t>Application should handle concurrent access without data corruption</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verify security - access control</t>
+          <t>Verify browser compatibility</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Attempt to access admin features as user</t>
+          <t>Access application on different browsers (Chrome, Firefox, Safari, Edge)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Admin features remain inaccessible</t>
+          <t>Application should function correctly on all major browsers</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verify form validation</t>
+          <t>Verify security - direct URL access without login</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submit empty username/password</t>
+          <t>Try to access main application URL directly</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Form prevents submission with appropriate feedback</t>
+          <t>User should be redirected to login page</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Verify accessibility compliance</t>
+          <t>Verify application behavior with large datasets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Test with screen reader</t>
+          <t>Load table with 100+ rows</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>All elements are properly accessible</t>
+          <t>Application should handle large datasets without significant performance degradation</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Verify data integrity</t>
+          <t>Verify text area resizing functionality</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Save data with special characters</t>
+          <t>Enter large amounts of text in text areas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Data is saved and retrieved correctly</t>
+          <t>Text areas should resize appropriately to accommodate content</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verify file system permissions</t>
+          <t>Verify accessibility compliance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Save data with insufficient permissions</t>
+          <t>Check application with accessibility tools</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Appropriate error message displayed</t>
+          <t>Application should meet WCAG 2.1 AA standards</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Verify concurrent user access</t>
+          <t>Verify data validation for date fields</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Multiple users accessing simultaneously</t>
+          <t>Enter invalid date format in Week Range field</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Data integrity is maintained</t>
+          <t>Application should validate and reject invalid date formats</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,17 +424,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Test Condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Test Cases</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Expected Output</t>
+          <t>Expected Results</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -451,22 +451,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-F-001</t>
+          <t>TC001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Verify successful login with admin credentials</t>
+          <t>Login functionality with valid admin credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Username: "admin"&lt;br&gt;Password: "admin123"</t>
+          <t>1. Enter username: "admin"&lt;br&gt;2. Enter password: "admin123"&lt;br&gt;3. Click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application view with admin controls visible</t>
+          <t>1. Login successful&lt;br&gt;2. Main application page is displayed&lt;br&gt;3. Admin controls (Add Row, Save buttons) are visible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -476,29 +476,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-F-002</t>
+          <t>TC002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verify successful login with user credentials</t>
+          <t>Login functionality with valid user credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Username: "user"&lt;br&gt;Password: "user123"</t>
+          <t>1. Enter username: "user"&lt;br&gt;2. Enter password: "user123"&lt;br&gt;3. Click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application view with read-only access (no admin controls)</t>
+          <t>1. Login successful&lt;br&gt;2. Main application page is displayed&lt;br&gt;3. Admin controls (Add Row, Save buttons) are hidden</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -508,29 +508,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-F-003</t>
+          <t>TC003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Verify login with invalid credentials</t>
+          <t>Login functionality with invalid credentials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Username: "invalid"&lt;br&gt;Password: "wrong"</t>
+          <t>1. Enter username: "invalid"&lt;br&gt;2. Enter password: "invalid"&lt;br&gt;3. Click Login button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>1. Alert message "Invalid credentials" is displayed&lt;br&gt;2. User remains on login page</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -540,29 +540,29 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-F-004</t>
+          <t>TC004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Verify logout functionality</t>
+          <t>Logout functionality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on Logout button</t>
+          <t>1. Login as any user&lt;br&gt;2. Click Logout button</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and returned to login screen</t>
+          <t>1. User is logged out&lt;br&gt;2. Login page is displayed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-F-005</t>
+          <t>TC005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Verify admin can add a new row</t>
+          <t>Add row functionality for admin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as admin and click "Add Row" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click "Add Row" button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>1. New row is added to the table&lt;br&gt;2. All fields in the new row are editable</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -611,22 +611,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-F-006</t>
+          <t>TC006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verify admin can delete a row</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Login as admin and click "Delete" button on a row</t>
+          <t>1. Login as admin&lt;br&gt;2. Add a row or edit existing row&lt;br&gt;3. Click on Week Range field</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The selected row should be removed from the table</t>
+          <t>1. Flatpickr date range picker opens&lt;br&gt;2. User can select a date range&lt;br&gt;3. Selected date range appears in the field</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-F-007</t>
+          <t>TC007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Verify admin can edit a row</t>
+          <t>Edit row functionality for admin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click "Edit" button on a row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click "Edit" button on an existing row</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The row should become editable, then save changes and become read-only again</t>
+          <t>1. Row fields become editable&lt;br&gt;2. Edit button changes to "Save"&lt;br&gt;3. After editing and clicking "Save", fields become read-only again</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-F-008</t>
+          <t>TC008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Verify admin can save the entire table</t>
+          <t>Delete row functionality for admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Make changes to table&lt;br&gt;3. Click "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click "Delete" button on an existing row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data should be saved to the server and success message displayed</t>
+          <t>1. Row is removed from the table</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -707,22 +707,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC-F-009</t>
+          <t>TC009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Verify date picker functionality</t>
+          <t>Save table functionality for admin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Click on Week Range input field</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click "Save" button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Date picker should appear allowing selection of date range</t>
+          <t>1. Data is sent to server&lt;br&gt;2. Success message is displayed&lt;br&gt;3. Data is saved to CSV file</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -739,22 +739,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC-F-010</t>
+          <t>TC010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verify user cannot edit table data</t>
+          <t>Read-only view for regular users</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Login as user and attempt to modify any field</t>
+          <t>1. Login as user&lt;br&gt;2. Attempt to edit any field in the table</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>All fields should be disabled/read-only</t>
+          <t>1. All fields are disabled/read-only&lt;br&gt;2. No edit, delete, add row or save buttons are visible</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -771,22 +771,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC-F-011</t>
+          <t>TC011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Verify table loads correctly on login</t>
+          <t>Data loading on login</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login with valid credentials</t>
+          <t>1. Ensure CSV file exists with data&lt;br&gt;2. Login as any user</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table should populate with data from the server</t>
+          <t>1. Table is populated with data from CSV file</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -796,29 +796,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC-F-012</t>
+          <t>TC012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Verify admin controls visibility for admin</t>
+          <t>Empty table handling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>1. Ensure CSV file is empty or doesn't exist&lt;br&gt;2. Login as any user</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"Add Row" and "Save" buttons should be visible</t>
+          <t>1. Empty table is displayed without errors</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,22 +835,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-F-013</t>
+          <t>TC013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verify admin controls invisibility for user</t>
+          <t>Save with empty data</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>1. Login as admin&lt;br&gt;2. Delete all rows or ensure table is empty&lt;br&gt;3. Click "Save" button</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"Add Row" and "Save" buttons should be hidden</t>
+          <t>1. Alert message "No data to save" is displayed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -867,22 +867,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-F-014</t>
+          <t>TC014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Verify saving empty table</t>
+          <t>Network path availability</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin, delete all rows, click "Save"</t>
+          <t>1. Disconnect network path&lt;br&gt;2. Login and attempt to save data</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>1. Error message is displayed when saving fails</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -899,22 +899,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-F-015</t>
+          <t>TC015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Verify data persistence after logout and login</t>
+          <t>Form validation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Make changes and save&lt;br&gt;3. Logout&lt;br&gt;4. Login again</t>
+          <t>1. Login as admin&lt;br&gt;2. Add a row but leave Week Range empty&lt;br&gt;3. Click "Save" button</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Changes should persist and be visible after logging in again</t>
+          <t>1. Row with empty Week Range is not saved</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -924,29 +924,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Verify application responsiveness</t>
+          <t>Responsiveness on different screen sizes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>1. Access application on desktop, tablet, and mobile devices</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Application should be responsive and usable on various screen sizes</t>
+          <t>1. UI adapts to different screen sizes&lt;br&gt;2. All elements remain usable and visible</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Verify application load time</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Open the application URL</t>
+          <t>1. Test application on Chrome, Firefox, Safari, and Edge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>1. Application functions correctly on all major browsers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verify error handling for network issues</t>
+          <t>Performance - load time</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Disconnect network and attempt to save data</t>
+          <t>1. Measure time to load application&lt;br&gt;2. Measure time to load data with 100+ rows</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>1. Application loads within 3 seconds&lt;br&gt;2. Data loads within 5 seconds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1027,22 +1027,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Verify concurrent user access</t>
+          <t>Security - authentication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Multiple users access the application simultaneously</t>
+          <t>1. Attempt to access main application without login&lt;br&gt;2. Attempt to access /data endpoint directly</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Application should handle concurrent access without data corruption</t>
+          <t>1. Access is denied without proper authentication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1059,22 +1059,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>TC020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Verify browser compatibility</t>
+          <t>Error handling - server errors</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Access application on different browsers (Chrome, Firefox, Safari, Edge)</t>
+          <t>1. Simulate server error during save operation&lt;br&gt;2. Observe application behavior</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Application should function correctly on all major browsers</t>
+          <t>1. Appropriate error message is displayed&lt;br&gt;2. Application remains usable</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1083,166 +1083,6 @@
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TC-NF-006</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Verify security - direct URL access without login</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Try to access main application URL directly</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>User should be redirected to login page</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TC-NF-007</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Verify application behavior with large datasets</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Load table with 100+ rows</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Application should handle large datasets without significant performance degradation</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TC-NF-008</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Verify text area resizing functionality</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Enter large amounts of text in text areas</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Text areas should resize appropriately to accommodate content</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TC-NF-009</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Verify accessibility compliance</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Check application with accessibility tools</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Application should meet WCAG 2.1 AA standards</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TC-NF-010</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Verify data validation for date fields</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Enter invalid date format in Week Range field</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Application should validate and reject invalid date formats</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Expected Results</t>
+          <t>Expected Output</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -456,17 +456,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials for admin</t>
+          <t>Login functionality with valid admin credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1. Enter username: "admin" &lt;br&gt; 2. Enter password: "admin123" &lt;br&gt; 3. Click Login button</t>
+          <t>1. Navigate to the application&lt;br&gt;2. Enter username: "admin"&lt;br&gt;3. Enter password: "admin123"&lt;br&gt;4. Click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Login form should disappear &lt;br&gt; 2. Main application should be displayed &lt;br&gt; 3. Admin controls (Add Row, Save buttons) should be visible</t>
+          <t>1. Login form disappears&lt;br&gt;2. Main application screen is displayed&lt;br&gt;3. Admin controls (Add Row, Save buttons) are visible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials for user</t>
+          <t>Login functionality with valid user credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Enter username: "user" &lt;br&gt; 2. Enter password: "user123" &lt;br&gt; 3. Click Login button</t>
+          <t>1. Navigate to the application&lt;br&gt;2. Enter username: "user"&lt;br&gt;3. Enter password: "user123"&lt;br&gt;4. Click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1. Login form should disappear &lt;br&gt; 2. Main application should be displayed &lt;br&gt; 3. Admin controls should be hidden &lt;br&gt; 4. Action column should be hidden</t>
+          <t>1. Login form disappears&lt;br&gt;2. Main application screen is displayed&lt;br&gt;3. Admin controls (Add Row, Save buttons) are hidden</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Enter invalid username and password &lt;br&gt; 2. Click Login button</t>
+          <t>1. Navigate to the application&lt;br&gt;2. Enter invalid username and password&lt;br&gt;3. Click Login button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" is displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Login as any user &lt;br&gt; 2. Click Logout button</t>
+          <t>1. Login to the application&lt;br&gt;2. Click Logout button</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1. Application should reload &lt;br&gt; 2. Login form should be displayed</t>
+          <t>Application reloads and login form is displayed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality for admin</t>
+          <t>Add Row functionality for admin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Click "Add Row" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Add Row button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New empty row should be added to the table with date picker and text areas</t>
+          <t>New empty row is added to the table with editable fields</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edit row functionality for admin</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Add a row or use existing row &lt;br&gt; 3. Click "Edit" button &lt;br&gt; 4. Modify data &lt;br&gt; 5. Click "Save" button (in row)</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Add Row button&lt;br&gt;3. Click on Week Range input field</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1. Fields should become editable when Edit is clicked &lt;br&gt; 2. Fields should become read-only when Save is clicked &lt;br&gt; 3. Modified data should be preserved</t>
+          <t>Flatpickr date range picker appears allowing date range selection</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delete row functionality for admin</t>
+          <t>Edit row functionality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Add a row or use existing row &lt;br&gt; 3. Click "Delete" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Edit button on an existing row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click Save button (on the row)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>1. Fields become editable when Edit is clicked&lt;br&gt;2. Fields become read-only when Save is clicked&lt;br&gt;3. Changes are preserved in the row</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save table functionality</t>
+          <t>Delete row functionality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Add/edit rows with data &lt;br&gt; 3. Click "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Delete button on an existing row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Data should be sent to server &lt;br&gt; 2. Success message should be displayed &lt;br&gt; 3. Data should persist on page reload</t>
+          <t>Row is removed from the table</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Save table functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Add a row &lt;br&gt; 3. Click on the date field</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1. Flatpickr date range picker should open &lt;br&gt; 2. User should be able to select a date range &lt;br&gt; 3. Selected range should appear in the field</t>
+          <t>1. Data is sent to server&lt;br&gt;2. Success message is displayed&lt;br&gt;3. Data persists after page reload</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Load table data on login</t>
+          <t>Load table functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Save some data to the table &lt;br&gt; 2. Logout and login again</t>
+          <t>1. Login to the application</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Previously saved data should be loaded and displayed in the table</t>
+          <t>Existing data is loaded from server and displayed in the table</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1. Login as user &lt;br&gt; 2. Try to edit existing data</t>
+          <t>1. Login as user&lt;br&gt;2. Attempt to edit fields in the table</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1. All fields should be disabled/read-only &lt;br&gt; 2. No edit, delete, add row or save buttons should be visible</t>
+          <t>All fields are disabled/read-only for user role</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Save with empty table</t>
+          <t>User permissions - no admin controls</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Clear all rows &lt;br&gt; 3. Click "Save" button</t>
+          <t>1. Login as user</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>Add Row, Save buttons and Actions column are not visible</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>API endpoint for retrieving data</t>
+          <t>Empty table save</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Send GET request to "/data" endpoint</t>
+          <t>1. Login as admin&lt;br&gt;2. Delete all rows&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JSON array of table data should be returned</t>
+          <t>Alert message "No data to save" is displayed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>API endpoint for saving data</t>
+          <t>Server error handling</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Send POST request to "/save" endpoint with valid JSON data</t>
+          <t>1. Login as admin&lt;br&gt;2. Modify network path to invalid location&lt;br&gt;3. Make changes and click Save</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1. Data should be saved to CSV file &lt;br&gt; 2. Success response should be returned</t>
+          <t>Error message is displayed to user</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -899,27 +899,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-F-015</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CSV file creation</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1. Login as admin &lt;br&gt; 2. Add data and save</t>
+          <t>Access application on different screen sizes (desktop, tablet, mobile)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1. CSV file should be created at specified network path &lt;br&gt; 2. File should contain header row and data rows</t>
+          <t>UI elements adjust appropriately to screen size</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -931,27 +931,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>1. Measure time to load application&lt;br&gt;2. Measure time to load data with 100+ rows</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt and remain usable on various screen sizes</t>
+          <t>1. Initial page load &lt; 3 seconds&lt;br&gt;2. Data load &lt; 5 seconds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -963,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Open the application in browser</t>
+          <t>Test application on Chrome, Firefox, Safari, Edge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>Application functions correctly on all major browsers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,27 +995,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Network path accessibility</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Test application on Chrome, Firefox, Safari, Edge</t>
+          <t>Verify the network path is accessible from different network segments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Application should work consistently across all major browsers</t>
+          <t>Network path can be accessed from all required locations</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1027,30 +1027,126 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC-NF-005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Network path availability</t>
+          <t>Security - authentication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1. Disconnect from network &lt;br&gt; 2. Try to save data</t>
+          <t>1. Test direct URL access without login&lt;br&gt;2. Test API endpoints without authentication</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed when network path is unavailable</t>
+          <t>Access is denied without proper authentication</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Non-functional</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC-NF-006</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Data validation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Enter extremely long text in text areas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Application handles long text appropriately without UI issues</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-NF-007</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CSV file integrity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1. Save data with special characters&lt;br&gt;2. Reload the application</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Special characters are preserved correctly</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-NF-008</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Concurrent user access</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Multiple users access the application simultaneously</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No data corruption or conflicts occur</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1. Navigate to the application&lt;br&gt;2. Enter username: "admin"&lt;br&gt;3. Enter password: "admin123"&lt;br&gt;4. Click Login button</t>
+          <t>Enter username: "admin" and password: "admin123"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Login form disappears&lt;br&gt;2. Main application view appears&lt;br&gt;3. Admin controls (Add Row, Save buttons) are visible</t>
+          <t>User should be logged in as admin with full access to all features including add row, save, and edit/delete buttons</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Navigate to the application&lt;br&gt;2. Enter username: "user"&lt;br&gt;3. Enter password: "user123"&lt;br&gt;4. Click Login button</t>
+          <t>Enter username: "user" and password: "user123"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1. Login form disappears&lt;br&gt;2. Main application view appears&lt;br&gt;3. Admin controls are hidden</t>
+          <t>User should be logged in as user with read-only access (no add row, save, or edit/delete buttons)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Navigate to the application&lt;br&gt;2. Enter invalid username/password combinations&lt;br&gt;3. Click Login button</t>
+          <t>Enter invalid username and password combinations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" appears</t>
+          <t>Error message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Login to the application&lt;br&gt;2. Click the Logout button</t>
+          <t>Click on the Logout button after logging in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Application reloads and returns to login screen</t>
+          <t>User should be logged out and redirected to the login page</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality (admin only)</t>
+          <t>Add row functionality for admin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click "Add Row" button</t>
+          <t>Login as admin and click "Add Row" button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>New empty row is added to the table with date picker and text areas</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Delete row functionality (admin only)</t>
+          <t>Date range picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Add a row or select existing row&lt;br&gt;3. Click "Delete" button on that row</t>
+          <t>Click on the week range field in a new row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Selected row is removed from the table</t>
+          <t>Date picker should open allowing selection of a date range</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edit row functionality (admin only)</t>
+          <t>Edit row functionality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click "Edit" button on a row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click "Save" button on that row</t>
+          <t>Login as admin, add a row, enter data, click "Edit" button</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1. Fields become editable when Edit is clicked&lt;br&gt;2. Fields become read-only when Save is clicked&lt;br&gt;3. Changes are preserved in the row</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save table functionality (admin only)</t>
+          <t>Save edited row</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click "Save" button</t>
+          <t>After editing a row, click "Save" button on that row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Data is sent to server&lt;br&gt;2. Success message appears&lt;br&gt;3. Data persists after page reload</t>
+          <t>Row should be saved with updated data and fields should become disabled</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Delete row functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Add a new row&lt;br&gt;3. Click on the Week Range field</t>
+          <t>Login as admin, add a row, click "Delete" button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flatpickr date range picker appears allowing date range selection</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Load data functionality</t>
+          <t>Save table functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Login to the application</t>
+          <t>Login as admin, add/edit rows, click "Save" button</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Existing data from CSV file is loaded and displayed in the table</t>
+          <t>All data should be saved to the server and confirmation message displayed</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>User role permissions - view only</t>
+          <t>Load table data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1. Login as user&lt;br&gt;2. Attempt to edit fields&lt;br&gt;3. Check for admin controls</t>
+          <t>Login as admin or user</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1. All fields are disabled/read-only&lt;br&gt;2. Admin controls (Add Row, Save, Edit, Delete) are not visible</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empty table save validation</t>
+          <t>Empty table save</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Clear all rows&lt;br&gt;3. Click "Save" button</t>
+          <t>Try to save with no data in the table</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" appears</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,27 +835,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC-F-013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>User permission restrictions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Access the application on different screen sizes and devices</t>
+          <t>Login as user and attempt to edit fields</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>UI elements adjust appropriately to different screen sizes</t>
+          <t>All fields should be disabled and not editable</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -867,27 +867,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC-F-014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Error handling - network failure</t>
+          <t>Admin controls visibility</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Disconnect network&lt;br&gt;3. Try to save data</t>
+          <t>Login as admin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Appropriate error message is displayed</t>
+          <t>Add Row and Save buttons should be visible</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -899,27 +899,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC-F-015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Error handling - server error</t>
+          <t>User controls visibility</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Modify server path to be invalid&lt;br&gt;3. Try to save data</t>
+          <t>Login as user</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error message is displayed with appropriate details</t>
+          <t>Add Row and Save buttons should be hidden</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Performance - load time</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Load the application and measure time until fully interactive</t>
+          <t>Access application on different screen sizes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Application loads within 3 seconds</t>
+          <t>UI should adapt appropriately to different screen sizes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Security - authentication</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1. Try to access main application without login&lt;br&gt;2. Try to access /data endpoint directly</t>
+          <t>Load the application with a large dataset</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Access is denied, redirected to login</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Security - XSS vulnerability</t>
+          <t>Error handling for network issues</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Enter script tags in text fields and try to save</t>
+          <t>Simulate network disconnection during save operation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Script tags are escaped or sanitized</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1027,22 +1027,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Usability - form validation</t>
+          <t>CSV file format integrity</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submit login form with empty fields</t>
+          <t>Save data and verify the CSV file format</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Appropriate validation messages appear</t>
+          <t>CSV file should have correct headers and data format</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1059,30 +1059,190 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>TC-NF-005</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cross-browser compatibility</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Test application on different browsers (Chrome, Firefox, Safari)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Application should work consistently across browsers</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC-NF-006</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Security - unauthorized access</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Attempt to access main application without login</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>User should not be able to access the main application</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC-NF-007</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data persistence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Save data, logout, and login again</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Previously saved data should be displayed correctly</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>TC-NF-008</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Compatibility - browser testing</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Test application on Chrome, Firefox, Safari, and Edge</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Application functions correctly on all browsers</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Input validation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Enter extremely long text in text areas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Application should handle long text appropriately without breaking the UI</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC-NF-009</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Special characters handling</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Enter special characters in text fields</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Application should handle special characters correctly</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-NF-010</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Concurrent user access</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Multiple users access the application simultaneously</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Application should handle concurrent access without data corruption</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Non-functional</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password combinations</t>
+          <t>Enter invalid username and password</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date range picker functionality</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click on the week range field in a new row</t>
+          <t>Click on the Week Range field in a new row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Date picker should open allowing selection of a date range</t>
+          <t>Date picker should open allowing selection of date range</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Row should become editable</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save edited row</t>
+          <t>Save row edits</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>After editing a row, click "Save" button on that row</t>
+          <t>After editing a row, click "Save" button in the row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should be saved with updated data and fields should become disabled</t>
+          <t>Row should become non-editable with saved changes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>All data should be saved to the server and confirmation message displayed</t>
+          <t>Data should be saved to the server with success message</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empty table save</t>
+          <t>Read-only mode for user</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Try to save with no data in the table</t>
+          <t>Login as user and verify all fields</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>All fields should be disabled/read-only</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>User permission restrictions</t>
+          <t>Admin controls visibility</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as user and attempt to edit fields</t>
+          <t>Login as admin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>All fields should be disabled and not editable</t>
+          <t>Add Row and Save buttons should be visible</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Admin controls visibility</t>
+          <t>User controls visibility</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>Login as user</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be visible</t>
+          <t>Add Row and Save buttons should be hidden</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>User controls visibility</t>
+          <t>Empty table save</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>Login as admin, clear all rows, click "Save"</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be hidden</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt appropriately to different screen sizes</t>
+          <t>UI should adapt to different screen sizes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Error handling for network issues</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Simulate network disconnection during save operation</t>
+          <t>Test on Chrome, Firefox, Safari, Edge</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Application should work consistently across all browsers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CSV file format integrity</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Save data and verify the CSV file format</t>
+          <t>Simulate network error during save operation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CSV file should have correct headers and data format</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cross-browser compatibility</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Test application on different browsers (Chrome, Firefox, Safari)</t>
+          <t>Attempt to access main application without login</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Application should work consistently across browsers</t>
+          <t>User should not be able to access the application without authentication</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Security - unauthorized access</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>Login as user and attempt to modify data</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>User should not be able to access the main application</t>
+          <t>User should not be able to modify data</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Previously saved data should be displayed correctly</t>
+          <t>Previously saved data should be displayed</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Input validation</t>
+          <t>UI aesthetics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enter extremely long text in text areas</t>
+          <t>Verify UI elements alignment and styling</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Application should handle long text appropriately without breaking the UI</t>
+          <t>UI elements should be properly aligned and styled</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Special characters handling</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enter special characters in text fields</t>
+          <t>Test with screen readers and keyboard navigation</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Application should handle special characters correctly</t>
+          <t>Application should be accessible via keyboard and screen readers</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Concurrent user access</t>
+          <t>Concurrent users</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Multiple users access the application simultaneously</t>
+          <t>Multiple users accessing the application simultaneously</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Application should handle concurrent access without data corruption</t>
+          <t>Application should handle concurrent users without data corruption</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid admin credentials</t>
+          <t>Login Functionality - Valid Credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin" and password: "admin123"</t>
+          <t>1. Enter username "admin" and password "admin123"&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in as admin with full access to all features including add row, save, and edit/delete buttons</t>
+          <t>User should be logged in as admin with full access to the application</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid user credentials</t>
+          <t>Login Functionality - Valid Credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user" and password: "user123"</t>
+          <t>1. Enter username "user" and password "user123"&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in as user with read-only access (no add row, save, or edit/delete buttons)</t>
+          <t>User should be logged in as user with read-only access to the application</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Login functionality with invalid credentials</t>
+          <t>Login Functionality - Invalid Credentials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password</t>
+          <t>1. Enter invalid username and password&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Logout functionality</t>
+          <t>Admin Role Permissions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on the Logout button after logging in</t>
+          <t>1. Login as admin&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to the login page</t>
+          <t>Add Row button, Save button, and Actions column should be visible</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality for admin</t>
+          <t>User Role Permissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as admin and click "Add Row" button</t>
+          <t>1. Login as user&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>Add Row button, Save button, and Actions column should be hidden</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Add Row Functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click on the Week Range field in a new row</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Add Row button</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Date picker should open allowing selection of date range</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edit row functionality</t>
+          <t>Date Range Picker</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, enter data, click "Edit" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Add a new row&lt;br&gt;3. Click on Week Range field</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row should become editable</t>
+          <t>Date range picker should appear allowing selection of start and end dates</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save row edits</t>
+          <t>Edit Row Functionality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>After editing a row, click "Save" button in the row</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Edit button on an existing row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should become non-editable with saved changes</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delete row functionality</t>
+          <t>Save Edit Functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click "Delete" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Edit button on a row&lt;br&gt;3. Make changes&lt;br&gt;4. Click Save button (in the row)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Changes should be saved and fields should become non-editable</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Save table functionality</t>
+          <t>Delete Row Functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Login as admin, add/edit rows, click "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Delete button on a row</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Data should be saved to the server with success message</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Load table data</t>
+          <t>Save Table Functionality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login as admin or user</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>Data should be saved to the server and success message displayed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Read-only mode for user</t>
+          <t>Save Empty Table</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login as user and verify all fields</t>
+          <t>1. Login as admin&lt;br&gt;2. Delete all rows&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>All fields should be disabled/read-only</t>
+          <t>Alert message "No data to save." should be displayed</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Admin controls visibility</t>
+          <t>Data Loading</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>1. Login as admin or user</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be visible</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>User controls visibility</t>
+          <t>Logout Functionality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>1. Login as admin or user&lt;br&gt;2. Click Logout button</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be hidden</t>
+          <t>User should be logged out and returned to the login screen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empty table save</t>
+          <t>Read-only Mode for User</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Login as admin, clear all rows, click "Save"</t>
+          <t>1. Login as user&lt;br&gt;2. Try to edit any field in the table</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>All fields should be disabled and non-editable</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -931,27 +931,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC-F-016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Empty Field Validation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>1. Login as admin&lt;br&gt;2. Add a row without entering Week Range&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt to different screen sizes</t>
+          <t>Row with empty Week Range should not be saved</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -963,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Load the application with a large dataset</t>
+          <t>1. Access application on different screen sizes&lt;br&gt;2. Verify layout adjusts appropriately</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>UI should adapt to different screen sizes while maintaining usability</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,27 +995,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Load Time Performance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Test on Chrome, Firefox, Safari, Edge</t>
+          <t>1. Measure time taken to load the application&lt;br&gt;2. Measure time taken to load data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Application should work consistently across all browsers</t>
+          <t>Application should load within 3 seconds&lt;br&gt;Data should load within 2 seconds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1027,27 +1027,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Browser Compatibility</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Simulate network error during save operation</t>
+          <t>Test application on Chrome, Firefox, Safari, and Edge</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Application should function correctly on all major browsers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1059,27 +1059,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>1. Simulate network error during save operation&lt;br&gt;2. Observe error handling</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>User should not be able to access the application without authentication</t>
+          <t>Appropriate error message should be displayed to the user</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1091,27 +1091,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>TC-NF-005</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Login as user and attempt to modify data</t>
+          <t>1. Try to access main application without logging in&lt;br&gt;2. Try to bypass login by manipulating DOM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>User should not be able to modify data</t>
+          <t>Access should be denied, user should be redirected to login page</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1123,126 +1123,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>TC-NF-006</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Save data, logout, and login again</t>
+          <t>Try to perform admin actions while logged in as user by manipulating DOM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Previously saved data should be displayed</t>
+          <t>Actions should be rejected by the application</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Non-functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TC-NF-008</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UI aesthetics</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Verify UI elements alignment and styling</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>UI elements should be properly aligned and styled</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Non-functional</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TC-NF-009</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Test with screen readers and keyboard navigation</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Application should be accessible via keyboard and screen readers</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Non-functional</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TC-NF-010</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Concurrent users</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Multiple users accessing the application simultaneously</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Application should handle concurrent users without data corruption</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Non-functional</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,17 +456,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login Functionality - Valid Credentials</t>
+          <t>Login functionality with valid admin credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1. Enter username "admin" and password "admin123"&lt;br&gt;2. Click Login button</t>
+          <t>Enter username: "admin", password: "admin123" and click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in as admin with full access to the application</t>
+          <t>User should be logged in as admin with full access to all features including Add Row and Save buttons</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -488,17 +488,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login Functionality - Valid Credentials</t>
+          <t>Login functionality with valid user credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1. Enter username "user" and password "user123"&lt;br&gt;2. Click Login button</t>
+          <t>Enter username: "user", password: "user123" and click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in as user with read-only access to the application</t>
+          <t>User should be logged in as user with read-only access (no Add Row or Save buttons)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,17 +520,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Login Functionality - Invalid Credentials</t>
+          <t>Login functionality with invalid credentials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1. Enter invalid username and password&lt;br&gt;2. Click Login button</t>
+          <t>Enter invalid username and password combinations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>Error message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Admin Role Permissions</t>
+          <t>Logout functionality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
+          <t>Click on Logout button after logging in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Add Row button, Save button, and Actions column should be visible</t>
+          <t>User should be logged out and redirected to login page</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>User Role Permissions</t>
+          <t>Add row functionality for admin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. Login as user&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
+          <t>Login as admin and click "Add Row" button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Add Row button, Save button, and Actions column should be hidden</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logout Functionality</t>
+          <t>Date range picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1. Login to the application&lt;br&gt;2. Click Logout button</t>
+          <t>Click on the Week Range input field in a new row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to login page</t>
+          <t>Date range picker should appear allowing selection of start and end dates</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Add Row Functionality</t>
+          <t>Edit row functionality for admin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click Add Row button</t>
+          <t>Login as admin, add a row, enter data, click Edit button</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>Row should become editable/non-editable when Edit/Save button is clicked</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Date Range Picker</t>
+          <t>Delete row functionality for admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Add a new row&lt;br&gt;3. Click on Week Range field</t>
+          <t>Login as admin, add a row, click Delete button</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Date range picker should appear allowing selection of start and end dates</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edit Row Functionality</t>
+          <t>Save table data functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click Edit button on an existing row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click Save button</t>
+          <t>Login as admin, add rows with data, click Save button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Row should become editable, then save changes and become read-only again</t>
+          <t>Data should be saved to the server with success message</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Delete Row Functionality</t>
+          <t>Load table data functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Click Delete button on an existing row</t>
+          <t>Login as admin or user</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Save Table Functionality</t>
+          <t>Admin controls visibility for admin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click Save button</t>
+          <t>Login as admin</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Changes should be saved to the server and success message displayed</t>
+          <t>Add Row and Save buttons should be visible</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Save Empty Table</t>
+          <t>Admin controls visibility for user</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Delete all rows&lt;br&gt;3. Click Save button</t>
+          <t>Login as user</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alert message "No data to save." should be displayed</t>
+          <t>Add Row and Save buttons should be hidden</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data Loading</t>
+          <t>Actions column visibility for admin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1. Login to the application</t>
+          <t>Login as admin</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>Actions column should be visible with Edit and Delete buttons</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Read-only Access for User</t>
+          <t>Actions column visibility for user</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1. Login as user&lt;br&gt;2. Try to modify any field in the table</t>
+          <t>Login as user</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>All fields should be disabled and not editable</t>
+          <t>Actions column should be hidden</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data Persistence</t>
+          <t>Read-only fields for user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1. Login as admin&lt;br&gt;2. Make changes and save&lt;br&gt;3. Logout and login again</t>
+          <t>Login as user and check input fields</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Changes made should persist and be visible after re-login</t>
+          <t>All input fields should be disabled/read-only</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -931,27 +931,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC-F-016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive Design</t>
+          <t>Save with empty table</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Test application on different screen sizes and resolutions</t>
+          <t>Login as admin, ensure table is empty, click Save</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Application should be responsive and usable on different screen sizes</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -963,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC-F-017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Performance - Data Loading</t>
+          <t>Save with partially filled rows</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Measure time taken to load data when logging in</t>
+          <t>Login as admin, add row with only some fields filled, click Save</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Data should load within 3 seconds</t>
+          <t>Only rows with at least Week Range filled should be saved</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Performance - Save Operation</t>
+          <t>Page load performance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Measure time taken to save data</t>
+          <t>Load the application in browser</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Save operation should complete within 5 seconds</t>
+          <t>Page should load completely within 3 seconds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1027,22 +1027,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Attempt to access main application without logging in</t>
+          <t>Access application on different screen sizes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>User should not be able to access the application without authentication</t>
+          <t>UI should adapt to different screen sizes appropriately</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1059,22 +1059,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Login as user and attempt to perform admin actions via browser console</t>
+          <t>Test application on Chrome, Firefox, Safari, Edge</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>User should not be able to perform admin actions</t>
+          <t>Application should work consistently across all major browsers</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1091,22 +1091,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Usability - Form Validation</t>
+          <t>Error handling for network issues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submit login form with empty fields</t>
+          <t>Simulate network disconnection during save operation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Appropriate validation messages should be displayed</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1123,22 +1123,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>TC-NF-005</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Usability - Error Messages</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Test error handling when server is unavailable</t>
+          <t>Attempt to access main application without login</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>User-friendly error messages should be displayed</t>
+          <t>User should not be able to access the main application without authentication</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1155,22 +1155,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC-NF-008</t>
+          <t>TC-NF-006</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Compatibility - Browsers</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Test application on different browsers (Chrome, Firefox, Safari, Edge)</t>
+          <t>Login as user and attempt to modify data</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Application should work consistently across all major browsers</t>
+          <t>User should not be able to modify any data</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1187,30 +1187,126 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>TC-NF-007</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Data persistence</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Save data, logout, and login again</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Previously saved data should be correctly loaded</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC-NF-008</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UI aesthetics and usability</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Evaluate the visual appearance and ease of use</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UI should be visually appealing and intuitive to use</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>TC-NF-009</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Accessibility - Keyboard Navigation</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Navigate through the application using only keyboard</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>All functionality should be accessible via keyboard</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Concurrent user access</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Multiple users access the application simultaneously</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Application should handle concurrent access without data corruption</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Non-Functional</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC-NF-010</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Network path availability</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Check if the network path is accessible</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Application should handle scenarios where network path is unavailable</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,12 +461,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin", password: "admin123" and click Login button</t>
+          <t>Enter username: "admin" and password: "admin123"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in as admin with full access to all features including Add Row and Save buttons</t>
+          <t>User should be logged in successfully and redirected to the main application with admin controls visible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user", password: "user123" and click Login button</t>
+          <t>Enter username: "user" and password: "user123"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in as user with read-only access (no Add Row or Save buttons)</t>
+          <t>User should be logged in successfully and redirected to the main application with limited controls (no add/save buttons)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password combinations</t>
+          <t>Enter invalid username and password</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -557,12 +557,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on Logout button after logging in</t>
+          <t>Click on the Logout button after logging in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to login page</t>
+          <t>User should be logged out and returned to the login screen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date range picker functionality</t>
+          <t>Edit row functionality for admin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click on the Week Range input field in a new row</t>
+          <t>Login as admin, add a row, click "Edit" button on a row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Date range picker should appear allowing selection of start and end dates</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edit row functionality for admin</t>
+          <t>Delete row functionality for admin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, enter data, click Edit button</t>
+          <t>Login as admin, add a row, click "Delete" button on a row</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row should become editable/non-editable when Edit/Save button is clicked</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delete row functionality for admin</t>
+          <t>Save table functionality for admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click Delete button</t>
+          <t>Login as admin, add/edit data, click "Save" button</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Data should be saved to the server with success message</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Save table data functionality</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Login as admin, add rows with data, click Save button</t>
+          <t>Click on the Week Range input field</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Data should be saved to the server with success message</t>
+          <t>Date picker should appear allowing date range selection</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Load table data functionality</t>
+          <t>Load table data on login</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Login as admin or user</t>
+          <t>Login with valid credentials</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Admin controls visibility for admin</t>
+          <t>User role permissions - admin</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be visible</t>
+          <t>Admin should see and be able to use Add Row, Save, Edit, and Delete buttons</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Admin controls visibility for user</t>
+          <t>User role permissions - user</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Add Row and Save buttons should be hidden</t>
+          <t>User should not see Add Row, Save buttons, and should not be able to edit or delete rows</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Actions column visibility for admin</t>
+          <t>Empty table save</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>Login as admin, clear all rows, click Save</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Actions column should be visible with Edit and Delete buttons</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Actions column visibility for user</t>
+          <t>API endpoint - GET /data</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>Send GET request to /data endpoint</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Actions column should be hidden</t>
+          <t>Server should return JSON array of table data</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Read-only fields for user</t>
+          <t>API endpoint - POST /save</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Login as user and check input fields</t>
+          <t>Send POST request to /save with valid data</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>All input fields should be disabled/read-only</t>
+          <t>Server should save data and return success message</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -931,27 +931,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-F-016</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Save with empty table</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Login as admin, ensure table is empty, click Save</t>
+          <t>Access application on different screen sizes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>UI should adapt and remain usable across different screen sizes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -963,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-F-017</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Save with partially filled rows</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Login as admin, add row with only some fields filled, click Save</t>
+          <t>Load the application with 100+ rows of data</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Only rows with at least Week Range filled should be saved</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Page load performance</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Load the application in browser</t>
+          <t>Test application on Chrome, Firefox, Safari, Edge</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Page should load completely within 3 seconds</t>
+          <t>Application should function correctly on all major browsers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1027,22 +1027,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Error handling - network failure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>Simulate network failure during save operation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UI should adapt to different screen sizes appropriately</t>
+          <t>User-friendly error message should be displayed</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1059,22 +1059,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>TC-NF-005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Security - authentication</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Test application on Chrome, Firefox, Safari, Edge</t>
+          <t>Attempt to access main application without login</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Application should work consistently across all major browsers</t>
+          <t>User should be redirected to login page</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1091,22 +1091,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>TC-NF-006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Error handling for network issues</t>
+          <t>Security - authorization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Simulate network disconnection during save operation</t>
+          <t>Login as user and attempt to perform admin actions via API</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Server should reject unauthorized actions</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1123,22 +1123,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>TC-NF-007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>Check application with accessibility tools</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>User should not be able to access the main application without authentication</t>
+          <t>Application should meet WCAG 2.1 AA standards</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1155,22 +1155,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>TC-NF-008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Data validation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Login as user and attempt to modify data</t>
+          <t>Enter extremely long text in text areas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>User should not be able to modify any data</t>
+          <t>Application should handle or limit input appropriately</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>TC-NF-009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Concurrent users</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Save data, logout, and login again</t>
+          <t>Simulate multiple users accessing and editing data simultaneously</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Previously saved data should be correctly loaded</t>
+          <t>Application should handle concurrent access without data corruption</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1219,22 +1219,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TC-NF-008</t>
+          <t>TC-NF-010</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UI aesthetics and usability</t>
+          <t>Network path availability</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Evaluate the visual appearance and ease of use</t>
+          <t>Test when network path is unavailable</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>UI should be visually appealing and intuitive to use</t>
+          <t>Application should display appropriate error message</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1243,70 +1243,6 @@
         </is>
       </c>
       <c r="F26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TC-NF-009</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Concurrent user access</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Multiple users access the application simultaneously</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Application should handle concurrent access without data corruption</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TC-NF-010</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Network path availability</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Check if the network path is accessible</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Application should handle scenarios where network path is unavailable</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Results123</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Results</t>
         </is>
       </c>
@@ -451,22 +456,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-F-001</t>
+          <t>F001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid admin credentials</t>
+          <t>Login functionality with valid credentials (admin)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin" and password: "admin123"</t>
+          <t>Enter username: "admin", password: "admin123" and click Login</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application with admin controls visible</t>
+          <t>User should be logged in and redirected to the main application with admin privileges</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -475,6 +480,11 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -483,22 +493,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-F-002</t>
+          <t>F002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid user credentials</t>
+          <t>Login functionality with valid credentials (user)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user" and password: "user123"</t>
+          <t>Enter username: "user", password: "user123" and click Login</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application with limited controls (no add/save buttons)</t>
+          <t>User should be logged in and redirected to the main application with user privileges (no add/save buttons)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -507,6 +517,11 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -515,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-F-003</t>
+          <t>F003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,12 +540,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password</t>
+          <t>Enter invalid username and password and click Login</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,6 +554,11 @@
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -547,7 +567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-F-004</t>
+          <t>F004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -557,12 +577,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on the Logout button after logging in</t>
+          <t>Click on Logout button after logging in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and returned to the login screen</t>
+          <t>User should be logged out and redirected to login page</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,6 +591,11 @@
         </is>
       </c>
       <c r="F5" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -579,12 +604,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-F-005</t>
+          <t>F005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality for admin</t>
+          <t>Add row functionality (admin only)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -603,6 +628,11 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -611,22 +641,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-F-006</t>
+          <t>F006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edit row functionality for admin</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click "Edit" button on a row</t>
+          <t>Click on the Week Range input field</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Date picker should appear allowing date range selection</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -635,6 +665,11 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -643,22 +678,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-F-007</t>
+          <t>F007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delete row functionality for admin</t>
+          <t>Edit row functionality (admin only)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click "Delete" button on a row</t>
+          <t>Login as admin, add a row, click "Edit" button</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -667,6 +702,11 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -675,22 +715,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-F-008</t>
+          <t>F008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save table functionality for admin</t>
+          <t>Save edited row (admin only)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Login as admin, add/edit data, click "Save" button</t>
+          <t>After editing a row, click "Save" button</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data should be saved to the server with success message</t>
+          <t>Row should be saved with edited content and fields should become disabled</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -699,6 +739,11 @@
         </is>
       </c>
       <c r="F9" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -707,22 +752,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC-F-009</t>
+          <t>F009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Delete row functionality (admin only)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Click on the Week Range input field</t>
+          <t>Login as admin, add a row, click "Delete" button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Date picker should appear allowing date range selection</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -731,6 +776,11 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -739,22 +789,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC-F-010</t>
+          <t>F010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Load table data on login</t>
+          <t>Save table functionality (admin only)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Login with valid credentials</t>
+          <t>Login as admin, add/edit rows, click "Save" button</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>Data should be saved to the server and success message displayed</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -763,6 +813,11 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -771,22 +826,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC-F-011</t>
+          <t>F011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>User role permissions - admin</t>
+          <t>Load table data</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login as admin</t>
+          <t>Login to the application</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Admin should see and be able to use Add Row, Save, Edit, and Delete buttons</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -795,6 +850,11 @@
         </is>
       </c>
       <c r="F12" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -803,22 +863,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC-F-012</t>
+          <t>F012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>User role permissions - user</t>
+          <t>User role restrictions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login as user</t>
+          <t>Login as user and attempt to add/edit/delete rows</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>User should not see Add Row, Save buttons, and should not be able to edit or delete rows</t>
+          <t>User should not be able to modify data (buttons hidden, fields disabled)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -827,6 +887,11 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -835,7 +900,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-F-013</t>
+          <t>F013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -845,7 +910,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as admin, clear all rows, click Save</t>
+          <t>Login as admin, delete all rows, click "Save" button</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -859,6 +924,11 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -867,22 +937,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-F-014</t>
+          <t>F014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>API endpoint - GET /data</t>
+          <t>Data persistence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Send GET request to /data endpoint</t>
+          <t>Login as admin, add data, save, logout, and login again</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Server should return JSON array of table data</t>
+          <t>Previously saved data should be displayed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -891,6 +961,11 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -899,30 +974,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-F-015</t>
+          <t>NF001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>API endpoint - POST /save</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Send POST request to /save with valid data</t>
+          <t>Access application on different screen sizes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Server should save data and return success message</t>
+          <t>UI should adapt to different screen sizes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -931,22 +1011,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>NF002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>Load the application with 100+ rows of data</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt and remain usable across different screen sizes</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -955,6 +1035,11 @@
         </is>
       </c>
       <c r="F17" t="inlineStr">
+        <is>
+          <t>❌ **Fail**</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -963,22 +1048,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>NF003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Load the application with 100+ rows of data</t>
+          <t>Test application on Chrome, Firefox, Safari, Edge</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>Application should work consistently across all browsers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -987,6 +1072,11 @@
         </is>
       </c>
       <c r="F18" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -995,22 +1085,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>NF004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Error handling</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Test application on Chrome, Firefox, Safari, Edge</t>
+          <t>Simulate network error during save operation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Application should function correctly on all major browsers</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1019,6 +1109,11 @@
         </is>
       </c>
       <c r="F19" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1027,22 +1122,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>NF005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Error handling - network failure</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Simulate network failure during save operation</t>
+          <t>Attempt to access main application without logging in</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>User-friendly error message should be displayed</t>
+          <t>User should be redirected to login page</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1051,6 +1146,11 @@
         </is>
       </c>
       <c r="F20" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1059,22 +1159,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>NF006</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - authentication</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>Login as user and attempt to access admin features via console</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>User should be redirected to login page</t>
+          <t>Admin features should remain inaccessible</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1083,6 +1183,11 @@
         </is>
       </c>
       <c r="F21" t="inlineStr">
+        <is>
+          <t>❌ **Fail**</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1091,22 +1196,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>NF007</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Security - authorization</t>
+          <t>Usability - Form validation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Login as user and attempt to perform admin actions via API</t>
+          <t>Submit login form with empty fields</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Server should reject unauthorized actions</t>
+          <t>Form should validate and prevent submission</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1115,6 +1220,11 @@
         </is>
       </c>
       <c r="F22" t="inlineStr">
+        <is>
+          <t>❌ **Fail**</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1123,7 +1233,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>NF008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1133,12 +1243,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check application with accessibility tools</t>
+          <t>Test application with screen reader</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Application should meet WCAG 2.1 AA standards</t>
+          <t>Application should be navigable and usable with screen reader</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1147,6 +1257,11 @@
         </is>
       </c>
       <c r="F23" t="inlineStr">
+        <is>
+          <t>❌ **Fail**</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1155,22 +1270,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC-NF-008</t>
+          <t>NF009</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Data validation</t>
+          <t>Data integrity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enter extremely long text in text areas</t>
+          <t>Save large amount of text in textarea fields</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Application should handle or limit input appropriately</t>
+          <t>Data should be saved and retrieved correctly without truncation</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1179,6 +1294,11 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1187,22 +1307,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC-NF-009</t>
+          <t>NF010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Concurrent users</t>
+          <t>Network path availability</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Simulate multiple users accessing and editing data simultaneously</t>
+          <t>Test application when network path is unavailable</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Application should handle concurrent access without data corruption</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1212,37 +1332,10 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TC-NF-010</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Network path availability</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Test when network path is unavailable</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Application should display appropriate error message</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials (admin)</t>
+          <t>Login functionality with valid credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin", password: "admin123" and click Login</t>
+          <t>Login with username "admin" and password "admin123"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in and redirected to the main application with admin privileges</t>
+          <t>User should be logged in as admin with full access to the application</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials (user)</t>
+          <t>Login functionality with valid credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user", password: "user123" and click Login</t>
+          <t>Login with username "user" and password "user123"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in and redirected to the main application with user privileges (no add/save buttons)</t>
+          <t>User should be logged in as user with read-only access to the application</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password and click Login</t>
+          <t>Login with incorrect username and password</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>Error message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Logout functionality</t>
+          <t>Admin role permissions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on Logout button after logging in</t>
+          <t>Login as admin and verify all controls are visible</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to login page</t>
+          <t>Admin should see Add Row button, Save button, and Actions column</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -609,17 +609,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality (admin only)</t>
+          <t>User role permissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as admin and click "Add Row" button</t>
+          <t>Login as user and verify limited controls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>User should not see Add Row button, Save button, and Actions column</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Add row functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click on the Week Range input field</t>
+          <t>Login as admin and click "Add Row" button</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Date picker should appear allowing date range selection</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -683,17 +683,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Edit row functionality (admin only)</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click "Edit" button</t>
+          <t>Click on the Week Range field in a new row</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Date picker should open allowing selection of date range</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save edited row (admin only)</t>
+          <t>Edit row functionality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>After editing a row, click "Save" button</t>
+          <t>Click "Edit" button on an existing row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should be saved with edited content and fields should become disabled</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delete row functionality (admin only)</t>
+          <t>Save row functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click "Delete" button</t>
+          <t>Click "Save" button after editing a row</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Row fields should become non-editable and changes should be saved</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Save table functionality (admin only)</t>
+          <t>Delete row functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Login as admin, add/edit rows, click "Save" button</t>
+          <t>Click "Delete" button on an existing row</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Data should be saved to the server and success message displayed</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -831,17 +831,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Load table data</t>
+          <t>Save table functionality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login to the application</t>
+          <t>Add/edit data and click "Save" button</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>Data should be saved to the server and success message displayed</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>User role restrictions</t>
+          <t>Logout functionality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login as user and attempt to add/edit/delete rows</t>
+          <t>Click "Logout" button</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>User should not be able to modify data (buttons hidden, fields disabled)</t>
+          <t>User should be logged out and returned to login screen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empty table save</t>
+          <t>Data loading</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as admin, delete all rows, click "Save" button</t>
+          <t>Login to the application</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Empty table save</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin, add data, save, logout, and login again</t>
+          <t>Try to save with no data in the table</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Previously saved data should be displayed</t>
+          <t>Alert message "No data to save" should be displayed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -974,27 +974,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NF001</t>
+          <t>F015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Read-only mode for user</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>Login as user and try to modify data</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UI should adapt to different screen sizes</t>
+          <t>All fields should be disabled and non-editable</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1011,22 +1011,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NF002</t>
+          <t>NF001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Load the application with 100+ rows of data</t>
+          <t>Access the application on different screen sizes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>UI should adapt appropriately to different screen sizes</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>❌ **Fail**</t>
+          <t>✅ **Pass**</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1048,22 +1048,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NF003</t>
+          <t>NF002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Test application on Chrome, Firefox, Safari, Edge</t>
+          <t>Load the application with a large dataset</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should work consistently across all browsers</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NF004</t>
+          <t>NF003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1122,22 +1122,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NF005</t>
+          <t>NF004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Attempt to access main application without logging in</t>
+          <t>Test application on different browsers (Chrome, Firefox, Safari)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>User should be redirected to login page</t>
+          <t>Application should work consistently across browsers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>✅ **Pass**</t>
+          <t>❌ **Fail**</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1159,22 +1159,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NF006</t>
+          <t>NF005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Login as user and attempt to access admin features via console</t>
+          <t>Attempt to access main application without login</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Admin features should remain inaccessible</t>
+          <t>User should not be able to bypass login screen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>❌ **Fail**</t>
+          <t>✅ **Pass**</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1196,22 +1196,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NF007</t>
+          <t>NF006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Usability - Form validation</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submit login form with empty fields</t>
+          <t>Login as user and attempt to perform admin actions via console</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Form should validate and prevent submission</t>
+          <t>User should not be able to perform admin actions</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1233,22 +1233,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NF008</t>
+          <t>NF007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Data validation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Test application with screen reader</t>
+          <t>Enter extremely long text in text areas</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Application should be navigable and usable with screen reader</t>
+          <t>Application should handle long text appropriately without breaking UI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>❌ **Fail**</t>
+          <t>✅ **Pass**</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1270,22 +1270,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NF009</t>
+          <t>NF008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Data integrity</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Save large amount of text in textarea fields</t>
+          <t>Check application with screen reader</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Data should be saved and retrieved correctly without truncation</t>
+          <t>Application should be accessible to users with disabilities</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>✅ **Pass**</t>
+          <t>❌ **Fail**</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1307,35 +1307,72 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>NF009</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Network path availability</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Test application when network path is unavailable</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Application should display appropriate error message</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>NF010</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Network path availability</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Test application when network path is unavailable</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Appropriate error message should be displayed</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Concurrent users</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Multiple users accessing the application simultaneously</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Application should handle concurrent access without data corruption</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Non-Functional</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>✅ **Pass**</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Results123</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>Results</t>
         </is>
       </c>
@@ -456,22 +451,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F001</t>
+          <t>TC-F-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials</t>
+          <t>Login functionality with valid admin credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Login with username "admin" and password "admin123"</t>
+          <t>Enter username: "admin" and password: "admin123"</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in as admin with full access to the application</t>
+          <t>User should be logged in successfully and redirected to the main application with admin privileges (Add Row and Save buttons visible)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -480,11 +475,6 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -493,22 +483,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F002</t>
+          <t>TC-F-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid credentials</t>
+          <t>Login functionality with valid user credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Login with username "user" and password "user123"</t>
+          <t>Enter username: "user" and password: "user123"</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in as user with read-only access to the application</t>
+          <t>User should be logged in successfully and redirected to the main application with user privileges (Add Row and Save buttons hidden)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,11 +507,6 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -530,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>TC-F-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Login with incorrect username and password</t>
+          <t>Enter invalid username and password</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" should be displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -554,11 +539,6 @@
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -567,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F004</t>
+          <t>TC-F-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Admin role permissions</t>
+          <t>Logout functionality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Login as admin and verify all controls are visible</t>
+          <t>Click on the Logout button after logging in</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Admin should see Add Row button, Save button, and Actions column</t>
+          <t>User should be logged out and redirected to the login page</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -591,11 +571,6 @@
         </is>
       </c>
       <c r="F5" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -604,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F005</t>
+          <t>TC-F-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>User role permissions</t>
+          <t>Add row functionality for admin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as user and verify limited controls</t>
+          <t>Login as admin and click on "Add Row" button</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>User should not see Add Row button, Save button, and Actions column</t>
+          <t>A new empty row should be added to the table</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -628,11 +603,6 @@
         </is>
       </c>
       <c r="F6" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -641,22 +611,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F006</t>
+          <t>TC-F-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Add row functionality</t>
+          <t>Edit row functionality for admin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Login as admin and click "Add Row" button</t>
+          <t>Login as admin, add a row, click on "Edit" button for that row</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>Row fields should become editable</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -665,11 +635,6 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -678,22 +643,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F007</t>
+          <t>TC-F-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Save edited row functionality for admin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Click on the Week Range field in a new row</t>
+          <t>After editing a row, click on "Save" button for that row</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Date picker should open allowing selection of date range</t>
+          <t>Row fields should become non-editable and changes should be saved</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -702,11 +667,6 @@
         </is>
       </c>
       <c r="F8" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -715,22 +675,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F008</t>
+          <t>TC-F-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Edit row functionality</t>
+          <t>Delete row functionality for admin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Click "Edit" button on an existing row</t>
+          <t>Login as admin, add a row, click on "Delete" button for that row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Row should be removed from the table</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -739,11 +699,6 @@
         </is>
       </c>
       <c r="F9" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -752,22 +707,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F009</t>
+          <t>TC-F-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Save row functionality</t>
+          <t>Save table functionality for admin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Click "Save" button after editing a row</t>
+          <t>Login as admin, add/edit rows, click on "Save" button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Row fields should become non-editable and changes should be saved</t>
+          <t>Data should be saved to the server and success message displayed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -776,11 +731,6 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -789,22 +739,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F010</t>
+          <t>TC-F-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Delete row functionality</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Click "Delete" button on an existing row</t>
+          <t>Click on the Week Range input field</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Date picker should appear allowing date range selection</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -813,11 +763,6 @@
         </is>
       </c>
       <c r="F11" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -826,22 +771,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F011</t>
+          <t>TC-F-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Save table functionality</t>
+          <t>Load table data on login</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Add/edit data and click "Save" button</t>
+          <t>Login with valid credentials</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Data should be saved to the server and success message displayed</t>
+          <t>Existing data should be loaded from the server and displayed in the table</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -850,11 +795,6 @@
         </is>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -863,22 +803,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F012</t>
+          <t>TC-F-012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Logout functionality</t>
+          <t>User permission restrictions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Click "Logout" button</t>
+          <t>Login as user and attempt to edit table data</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>User should be logged out and returned to login screen</t>
+          <t>All fields should be disabled/read-only for user role</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -887,11 +827,6 @@
         </is>
       </c>
       <c r="F13" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -900,22 +835,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F013</t>
+          <t>TC-F-013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data loading</t>
+          <t>Admin permission capabilities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login to the application</t>
+          <t>Login as admin and attempt to edit table data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>All fields should be editable for admin role</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -924,11 +859,6 @@
         </is>
       </c>
       <c r="F14" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -937,17 +867,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F014</t>
+          <t>TC-F-014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Empty table save</t>
+          <t>Save empty table</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Try to save with no data in the table</t>
+          <t>Login as admin, delete all rows, and click "Save"</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -961,11 +891,6 @@
         </is>
       </c>
       <c r="F15" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -974,35 +899,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F015</t>
+          <t>TC-NF-001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Read-only mode for user</t>
+          <t>Application responsiveness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Login as user and try to modify data</t>
+          <t>Access the application on different screen sizes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>All fields should be disabled and non-editable</t>
+          <t>Application should be responsive and maintain usability across different screen sizes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Non-Functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1011,22 +931,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NF001</t>
+          <t>TC-NF-002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Load time performance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access the application on different screen sizes</t>
+          <t>Measure the time taken to load the application</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt appropriately to different screen sizes</t>
+          <t>Application should load within 3 seconds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1035,11 +955,6 @@
         </is>
       </c>
       <c r="F17" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1048,22 +963,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NF002</t>
+          <t>TC-NF-003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Data load performance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Load the application with a large dataset</t>
+          <t>Measure the time taken to load data from server</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>Data should load within 2 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1072,11 +987,6 @@
         </is>
       </c>
       <c r="F18" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1085,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NF003</t>
+          <t>TC-NF-004</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Error handling</t>
+          <t>Save operation performance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Simulate network error during save operation</t>
+          <t>Measure the time taken to save data to server</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Save operation should complete within 3 seconds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1109,11 +1019,6 @@
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1122,7 +1027,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NF004</t>
+          <t>TC-NF-005</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1132,12 +1037,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Test application on different browsers (Chrome, Firefox, Safari)</t>
+          <t>Test the application on different browsers (Chrome, Firefox, Safari, Edge)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Application should work consistently across browsers</t>
+          <t>Application should work consistently across all major browsers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1146,11 +1051,6 @@
         </is>
       </c>
       <c r="F20" t="inlineStr">
-        <is>
-          <t>❌ **Fail**</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1159,22 +1059,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NF005</t>
+          <t>TC-NF-006</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Error handling for network issues</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>Simulate network disconnection during save operation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>User should not be able to bypass login screen</t>
+          <t>Appropriate error message should be displayed</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1183,11 +1083,6 @@
         </is>
       </c>
       <c r="F21" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1196,22 +1091,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NF006</t>
+          <t>TC-NF-007</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Login as user and attempt to perform admin actions via console</t>
+          <t>Attempt to access main application without logging in</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>User should not be able to perform admin actions</t>
+          <t>User should not be able to access the main application</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1220,11 +1115,6 @@
         </is>
       </c>
       <c r="F22" t="inlineStr">
-        <is>
-          <t>❌ **Fail**</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1233,22 +1123,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NF007</t>
+          <t>TC-NF-008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data validation</t>
+          <t>Security - Authorization</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Enter extremely long text in text areas</t>
+          <t>Login as user and attempt to access admin functions via console or URL manipulation</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Application should handle long text appropriately without breaking UI</t>
+          <t>User should not be able to perform admin actions</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1257,11 +1147,6 @@
         </is>
       </c>
       <c r="F23" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1270,22 +1155,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NF008</t>
+          <t>TC-NF-009</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Usability - Form validation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check application with screen reader</t>
+          <t>Submit login form with empty fields</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Application should be accessible to users with disabilities</t>
+          <t>Form should validate and prevent submission with empty fields</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1294,11 +1179,6 @@
         </is>
       </c>
       <c r="F24" t="inlineStr">
-        <is>
-          <t>❌ **Fail**</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -1307,22 +1187,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NF009</t>
+          <t>TC-NF-010</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Network path availability</t>
+          <t>Accessibility - Keyboard navigation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Test application when network path is unavailable</t>
+          <t>Navigate through the application using only keyboard</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Application should display appropriate error message</t>
+          <t>All functionality should be accessible via keyboard</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1331,48 +1211,6 @@
         </is>
       </c>
       <c r="F25" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NF010</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Concurrent users</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Multiple users accessing the application simultaneously</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Application should handle concurrent access without data corruption</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Non-Functional</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>✅ **Pass**</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,22 +451,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TC-F-001</t>
+          <t>F-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Login functionality with valid admin credentials</t>
+          <t>Login Functionality - Valid Credentials</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin" and password: "admin123"</t>
+          <t>1. Enter username "admin" and password "admin123"&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application with admin privileges (Add Row and Save buttons visible)</t>
+          <t>User should be logged in as admin with full access to the application&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -483,22 +483,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TC-F-002</t>
+          <t>F-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login functionality with valid user credentials</t>
+          <t>Login Functionality - Valid Credentials</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user" and password: "user123"</t>
+          <t>1. Enter username "user" and password "user123"&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in successfully and redirected to the main application with user privileges (Add Row and Save buttons hidden)</t>
+          <t>User should be logged in as user with read-only access to the application&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -515,22 +515,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TC-F-003</t>
+          <t>F-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Login functionality with invalid credentials</t>
+          <t>Login Functionality - Invalid Credentials</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password</t>
+          <t>1. Enter invalid username and/or password&lt;br&gt;2. Click Login button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" should be displayed&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,22 +547,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TC-F-004</t>
+          <t>F-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Logout functionality</t>
+          <t>Logout Functionality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on the Logout button after logging in</t>
+          <t>1. Login to the application&lt;br&gt;2. Click Logout button</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to the login page</t>
+          <t>User should be logged out and redirected to the login page&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -579,22 +579,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TC-F-005</t>
+          <t>F-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add row functionality for admin</t>
+          <t>Admin Role Permissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as admin and click on "Add Row" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table</t>
+          <t>Add Row button, Save button, and Actions column should be visible&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -611,22 +611,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TC-F-006</t>
+          <t>F-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Edit row functionality for admin</t>
+          <t>User Role Permissions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click on "Edit" button for that row</t>
+          <t>1. Login as user&lt;br&gt;2. Verify visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Add Row button, Save button, and Actions column should be hidden&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -643,22 +643,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TC-F-007</t>
+          <t>F-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Save edited row functionality for admin</t>
+          <t>Add Row Functionality</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>After editing a row, click on "Save" button for that row</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Add Row button</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row fields should become non-editable and changes should be saved</t>
+          <t>A new empty row should be added to the table&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TC-F-008</t>
+          <t>F-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delete row functionality for admin</t>
+          <t>Date Range Picker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Login as admin, add a row, click on "Delete" button for that row</t>
+          <t>1. Login as admin&lt;br&gt;2. Add a new row or edit existing row&lt;br&gt;3. Click on Week Range field</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Date range picker should appear allowing selection of start and end dates&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -707,22 +707,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TC-F-009</t>
+          <t>F-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Save table functionality for admin</t>
+          <t>Edit Row Functionality</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Login as admin, add/edit rows, click on "Save" button</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Edit button on an existing row&lt;br&gt;3. Modify fields&lt;br&gt;4. Click Save button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Data should be saved to the server and success message displayed</t>
+          <t>Row should become editable, then save changes and become read-only again&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -739,22 +739,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TC-F-010</t>
+          <t>F-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Delete Row Functionality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Click on the Week Range input field</t>
+          <t>1. Login as admin&lt;br&gt;2. Click Delete button on an existing row</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Date picker should appear allowing date range selection</t>
+          <t>Row should be removed from the table&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -771,22 +771,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TC-F-011</t>
+          <t>F-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Load table data on login</t>
+          <t>Save Table Functionality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Login with valid credentials</t>
+          <t>1. Login as admin&lt;br&gt;2. Make changes to the table&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from the server and displayed in the table</t>
+          <t>Data should be saved to the server and success message displayed&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -803,22 +803,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TC-F-012</t>
+          <t>F-012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>User permission restrictions</t>
+          <t>Save Table - Empty Data</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login as user and attempt to edit table data</t>
+          <t>1. Login as admin&lt;br&gt;2. Delete all rows or ensure no week range is entered&lt;br&gt;3. Click Save button</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>All fields should be disabled/read-only for user role</t>
+          <t>Alert message "No data to save." should be displayed&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -835,22 +835,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TC-F-013</t>
+          <t>F-013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Admin permission capabilities</t>
+          <t>Load Table Functionality</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as admin and attempt to edit table data</t>
+          <t>1. Login as admin or user</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>All fields should be editable for admin role</t>
+          <t>Existing data should be loaded from the server and displayed in the table&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -867,22 +867,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TC-F-014</t>
+          <t>F-014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Save empty table</t>
+          <t>Data Persistence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin, delete all rows, and click "Save"</t>
+          <t>1. Login as admin&lt;br&gt;2. Add/edit data and save&lt;br&gt;3. Logout and login again</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>Previously saved data should be displayed correctly&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -899,27 +899,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TC-NF-001</t>
+          <t>F-015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Application responsiveness</t>
+          <t>Read-only Mode for User</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Access the application on different screen sizes</t>
+          <t>1. Login as user&lt;br&gt;2. Try to edit any field in the table</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Application should be responsive and maintain usability across different screen sizes</t>
+          <t>All fields should be disabled and not editable&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Non-Functional</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -931,22 +931,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TC-NF-002</t>
+          <t>NF-001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Measure the time taken to load the application</t>
+          <t>Test the application on different screen sizes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>Application should be usable and properly displayed on different screen sizes&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -963,22 +963,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TC-NF-003</t>
+          <t>NF-002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data load performance</t>
+          <t>Performance - Load Time</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Measure the time taken to load data from server</t>
+          <t>Measure the time taken to load the application</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Data should load within 2 seconds</t>
+          <t>Application should load within 3 seconds&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -995,22 +995,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TC-NF-004</t>
+          <t>NF-003</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Save operation performance</t>
+          <t>Performance - Save Operation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Measure the time taken to save data to server</t>
+          <t>Measure the time taken to save data</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Save operation should complete within 3 seconds</t>
+          <t>Save operation should complete within 2 seconds&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1027,22 +1027,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TC-NF-005</t>
+          <t>NF-004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Security - Authentication</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Test the application on different browsers (Chrome, Firefox, Safari, Edge)</t>
+          <t>Attempt to access main application without logging in</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Application should work consistently across all major browsers</t>
+          <t>User should not be able to access the application without authentication&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1059,22 +1059,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TC-NF-006</t>
+          <t>NF-005</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Error handling for network issues</t>
+          <t>Security - Role-based Access</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Simulate network disconnection during save operation</t>
+          <t>Verify that user role permissions are enforced</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Users should only have access to features appropriate for their role&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1091,22 +1091,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TC-NF-007</t>
+          <t>NF-006</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Error Handling - Network Issues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Attempt to access main application without logging in</t>
+          <t>Test save functionality when network is unavailable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>User should not be able to access the main application</t>
+          <t>Appropriate error message should be displayed&lt;br&gt;❌ **Fail**</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1123,22 +1123,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TC-NF-008</t>
+          <t>NF-007</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Security - Authorization</t>
+          <t>Usability - Form Validation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Login as user and attempt to access admin functions via console or URL manipulation</t>
+          <t>Test form fields with invalid inputs</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>User should not be able to perform admin actions</t>
+          <t>Appropriate validation messages should be displayed&lt;br&gt;❌ **Fail**</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1155,22 +1155,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TC-NF-009</t>
+          <t>NF-008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Usability - Form validation</t>
+          <t>Compatibility - Browser Testing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submit login form with empty fields</t>
+          <t>Test application on different browsers (Chrome, Firefox, Safari, Edge)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Form should validate and prevent submission with empty fields</t>
+          <t>Application should work consistently across all major browsers&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TC-NF-010</t>
+          <t>NF-009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Accessibility - Keyboard navigation</t>
+          <t>Data Integrity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Navigate through the application using only keyboard</t>
+          <t>1. Save data&lt;br&gt;2. Verify saved data in CSV file</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>All functionality should be accessible via keyboard</t>
+          <t>Data in CSV file should match what was saved in the application&lt;br&gt;✅ **Pass**</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1211,6 +1211,38 @@
         </is>
       </c>
       <c r="F25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NF-010</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Test application with screen readers and keyboard navigation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Application should be accessible to users with disabilities&lt;br&gt;❌ **Fail**</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Non-Functional</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_case_results.xlsx
+++ b/test_case_results.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Enter username: "admin" and password: "admin123"</t>
+          <t>1. Enter username: "admin" &lt;br&gt; 2. Enter password: "admin123" &lt;br&gt; 3. Click Login button</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>User should be logged in as admin with access to all controls (Add Row, Save, Edit, Delete)</t>
+          <t>User successfully logs in and is directed to the main application page with admin controls visible</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -493,12 +493,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Enter username: "user" and password: "user123"</t>
+          <t>1. Enter username: "user" &lt;br&gt; 2. Enter password: "user123" &lt;br&gt; 3. Click Login button</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>User should be logged in as user with read-only access (no Add Row, Save, Edit, Delete buttons)</t>
+          <t>User successfully logs in and is directed to the main application page without admin controls</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enter invalid username and password</t>
+          <t>1. Enter username: "invalid" &lt;br&gt; 2. Enter password: "invalid" &lt;br&gt; 3. Click Login button</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alert message "Invalid credentials" should be displayed</t>
+          <t>Alert message "Invalid credentials" is displayed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Logout functionality</t>
+          <t>Admin role permissions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Click on Logout button after login</t>
+          <t>1. Login as admin &lt;br&gt; 2. Verify visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>User should be logged out and redirected to login page</t>
+          <t>Add Row button, Save button, and Actions column are visible</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -584,17 +584,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Add Row functionality for admin</t>
+          <t>User role permissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Login as admin and click "Add Row" button</t>
+          <t>1. Login as user &lt;br&gt; 2. Check visibility of Add Row, Save buttons and Actions column</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A new empty row should be added to the table with date picker and text areas</t>
+          <t>Add Row button, Save button, and Actions column are not visible</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Date picker functionality</t>
+          <t>Add new row functionality</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Click on Week Range input field</t>
+          <t>1. Login as admin &lt;br&gt; 2. Click Add Row button &lt;br&gt; 3. Fill in data in all fields &lt;br&gt; 4. Click Save button</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Date picker should appear allowing selection of date range</t>
+          <t>New row is added to the table with entered data</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Click "Edit" button on a row</t>
+          <t>1. Login as admin &lt;br&gt; 2. Click Edit button on an existing row &lt;br&gt; 3. Modify data &lt;br&gt; 4. Click Save button (in the row)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Row fields should become editable</t>
+          <t>Row data is updated with modified information</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -680,17 +680,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Save edited row</t>
+          <t>Delete row functionality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Click "Save" button after editing a row</t>
+          <t>1. Login as admin &lt;br&gt; 2. Click Delete button on an existing row</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Row should be saved with edited content and fields should become non-editable</t>
+          <t>Row is removed from the table</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delete row functionality</t>
+          <t>Save table data</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Click "Delete" button on a row</t>
+          <t>1. Login as admin &lt;br&gt; 2. Add/modify data &lt;br&gt; 3. Click Save button</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Row should be removed from the table</t>
+          <t>Alert message "Data saved successfully!" is displayed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Save table functionality with data</t>
+          <t>Load table data</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fill in at least one row and click "Save" button</t>
+          <t>1. Login as admin or user</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Data should be saved to server and success message displayed</t>
+          <t>Existing data from CSV file is loaded and displayed in the table</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Save table functionality with no data</t>
+          <t>Date picker functionality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Try to save with no rows or empty Week Range</t>
+          <t>1. Login as admin &lt;br&gt; 2. Click on Week Range input field</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alert message "No data to save" should be displayed</t>
+          <t>Date picker calendar appears allowing date range selection</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Load table data</t>
+          <t>Logout functionality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Login to application</t>
+          <t>1. Login as admin or user &lt;br&gt; 2. Click Logout button</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Existing data should be loaded from server and displayed in the table</t>
+          <t>User is logged out and returned to the login page</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>User permission restrictions</t>
+          <t>Save empty table</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Login as user and attempt to edit fields</t>
+          <t>1. Login as admin &lt;br&gt; 2. Delete all rows &lt;br&gt; 3. Click Save button</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>All fields should be disabled/read-only for user role</t>
+          <t>Alert message "No data to save." is displayed</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Admin permission capabilities</t>
+          <t>User edit restriction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Login as admin and verify all controls</t>
+          <t>1. Login as user &lt;br&gt; 2. Try to edit any field in the table</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Admin should have access to Add Row, Save, Edit, and Delete functionalities</t>
+          <t>All fields are disabled and cannot be edited</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -904,17 +904,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data persistence</t>
+          <t>Week Range validation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Save data, logout, and login again</t>
+          <t>1. Login as admin &lt;br&gt; 2. Add a row &lt;br&gt; 3. Leave Week Range empty &lt;br&gt; 4. Fill other fields &lt;br&gt; 5. Click Save</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Previously saved data should be displayed correctly</t>
+          <t>Row with empty Week Range is not saved</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -936,17 +936,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Responsive design</t>
+          <t>Response time for login</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Access application on different screen sizes</t>
+          <t>Measure time from clicking Login button to application loading</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>UI should adapt appropriately to different screen sizes</t>
+          <t>Login process completes within 3 seconds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Load time performance</t>
+          <t>Response time for data loading</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Load the application</t>
+          <t>Measure time from login to table data being displayed</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Application should load within 3 seconds</t>
+          <t>Table data loads within 5 seconds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1000,17 +1000,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Error handling for save operation</t>
+          <t>Response time for saving data</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Simulate network error during save</t>
+          <t>Measure time from clicking Save button to confirmation message</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Appropriate error message should be displayed</t>
+          <t>Save operation completes within 5 seconds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Security - Authentication</t>
+          <t>Browser compatibility</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Attempt to access main application without login</t>
+          <t>Test application on different browsers (Chrome, Firefox, Safari, Edge)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Main application should not be accessible without authentication</t>
+          <t>Application functions correctly on all major browsers</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1064,17 +1064,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Security - Role-based access</t>
+          <t>Responsive design</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Verify user and admin have appropriate access</t>
+          <t>Test application on different screen sizes and devices</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Controls should be displayed or hidden based on user role</t>
+          <t>UI elements adjust appropriately to different screen sizes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Browser compatibility</t>
+          <t>Error handling for network issues</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Test on different browsers (Chrome, Firefox, Safari)</t>
+          <t>Disconnect network while saving data</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Application should work consistently across browsers</t>
+          <t>Appropriate error message displayed when save operation fails</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Data validation</t>
+          <t>Security - password field</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Enter very large text in text areas</t>
+          <t>Check if password is masked</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Application should handle large text inputs without breaking</t>
+          <t>Password characters are displayed as dots/asterisks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Usability - UI elements</t>
+          <t>Security - session management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Verify all UI elements are properly visible and accessible</t>
+          <t>1. Login &lt;br&gt; 2. Close browser &lt;br&gt; 3. Reopen application</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>All buttons, inputs, and text should be clearly visible and accessible</t>
+          <t>User is required to login again (no persistent session)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Network path availability</t>
+          <t>Accessibility - keyboard navigation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Verify application can access the network path</t>
+          <t>Navigate through the application using only keyboard</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Application should be able to read/write to the specified network path</t>
+          <t>All functionality is accessible via keyboard</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1224,17 +1224,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CSV file format integrity</t>
+          <t>Performance with large datasets</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Save data and verify CSV structure</t>
+          <t>Load application with 100+ rows of data</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CSV file should maintain proper structure with headers and data</t>
+          <t>Application remains responsive with large datasets</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
